--- a/artfynd/A 34848-2020 artfynd.xlsx
+++ b/artfynd/A 34848-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34848-2020 artfynd.xlsx
+++ b/artfynd/A 34848-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8354,14 +8354,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>101930571</v>
+        <v>87398357</v>
       </c>
       <c r="B68" t="n">
         <v>96239</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8387,32 +8387,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gimån /800 m NO/, myrkant, Jmt</t>
+          <t>Gimån, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518845.4890740224</v>
+        <v>518845.9469225297</v>
       </c>
       <c r="R68" t="n">
-        <v>6965337.065940022</v>
+        <v>6965337.068568448</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8434,14 +8426,9 @@
           <t>Bräcke</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Z-Brä-1546</t>
-        </is>
-      </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-06-25</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
@@ -8451,7 +8438,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-06-25</t>
+          <t>2020-08-09</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -8461,7 +8448,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>299 florala.</t>
+          <t>Ett hundratal guckusko på 500 m2</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8477,19 +8464,15 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lars Grönvik</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8959,128 +8942,6 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>87398357</v>
-      </c>
-      <c r="B73" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>504</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Gimån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>518845.9469225297</v>
-      </c>
-      <c r="R73" t="n">
-        <v>6965337.068568448</v>
-      </c>
-      <c r="S73" t="n">
-        <v>25</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ett hundratal guckusko på 500 m2</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
